--- a/resultados_cluster/evaluated_metrics_detailed.xlsx
+++ b/resultados_cluster/evaluated_metrics_detailed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,16 +526,16 @@
         <v>0.993099985700665</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2205882352941176</v>
+        <v>0.2238805970149254</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0352133162532199</v>
+        <v>0.04768559514002881</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5156842694490399</v>
+        <v>0.5448283687746065</v>
       </c>
       <c r="M2" t="n">
-        <v>0.675249075554646</v>
+        <v>0.7794970064775397</v>
       </c>
     </row>
     <row r="3">
@@ -572,13 +572,13 @@
         <v>0.1515151515151515</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02688553773728895</v>
+        <v>0.04071133349842049</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5259620262246</v>
+        <v>0.6999407607724689</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6893658689021532</v>
+        <v>0.9563937680894565</v>
       </c>
     </row>
     <row r="4">
@@ -612,16 +612,16 @@
         <v>0.9932471170569911</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1791044776119403</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0376659542739044</v>
+        <v>0.05946589059909531</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5764217956363958</v>
+        <v>0.7600529880863236</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6614176320630516</v>
+        <v>0.9378363512304893</v>
       </c>
     </row>
     <row r="5">
@@ -658,13 +658,13 @@
         <v>0.1612903225806452</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01413726417603314</v>
+        <v>0.02278324198043638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6280342583080747</v>
+        <v>0.8929895389028973</v>
       </c>
       <c r="M5" t="n">
-        <v>0.677288759884662</v>
+        <v>0.9640523819373018</v>
       </c>
     </row>
     <row r="6">
@@ -701,13 +701,13 @@
         <v>0.1515151515151515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01296870005082408</v>
+        <v>0.01965203521006857</v>
       </c>
       <c r="L6" t="n">
-        <v>0.612181633696121</v>
+        <v>0.7454348885106756</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6347453450977432</v>
+        <v>0.8016415247223146</v>
       </c>
     </row>
     <row r="7">
@@ -744,13 +744,13 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7160618290622993</v>
+        <v>0.7438933710331348</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5789658414576615</v>
+        <v>0.7046916754322071</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7616582225229025</v>
+        <v>0.9968332745690844</v>
       </c>
     </row>
     <row r="8">
@@ -787,13 +787,13 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4757144909481237</v>
+        <v>0.720777947342757</v>
       </c>
       <c r="L8" t="n">
-        <v>0.628973434062513</v>
+        <v>0.8672551319595765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.722804723095005</v>
+        <v>0.9996998984705319</v>
       </c>
     </row>
     <row r="9">
@@ -827,16 +827,16 @@
         <v>0.9930699241883827</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9701492537313433</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8149532757718805</v>
+        <v>0.7522193673584197</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6381768485399762</v>
+        <v>0.9044543397930703</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6855558545808867</v>
+        <v>0.9907158211110132</v>
       </c>
     </row>
     <row r="10">
@@ -873,13 +873,13 @@
         <v>0.9838709677419355</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8042809299655158</v>
+        <v>0.7649625972394021</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6180024258478718</v>
+        <v>0.868605374810408</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6886667560815367</v>
+        <v>0.9923900421468482</v>
       </c>
     </row>
     <row r="11">
@@ -916,13 +916,13 @@
         <v>0.9848484848484849</v>
       </c>
       <c r="K11" t="n">
-        <v>0.827243639827235</v>
+        <v>0.7533945016790911</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5733759096265237</v>
+        <v>0.7555911659975677</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7406665924999219</v>
+        <v>0.9862711596429687</v>
       </c>
     </row>
     <row r="12">
@@ -956,16 +956,16 @@
         <v>0.9927951052333369</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8382352941176471</v>
+        <v>0.835820895522388</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7684264868870737</v>
+        <v>0.6743664759864558</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6650802759506605</v>
+        <v>0.9352396749905241</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7088608732483624</v>
+        <v>0.9981929288871252</v>
       </c>
     </row>
     <row r="13">
@@ -1002,13 +1002,13 @@
         <v>0.8939393939393939</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7792387457201748</v>
+        <v>0.6806870915672996</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6586418781297454</v>
+        <v>0.8396275710872777</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7350410281549888</v>
+        <v>0.9945092834419373</v>
       </c>
     </row>
     <row r="14">
@@ -1033,25 +1033,25 @@
         <v>0.9935437589670014</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8714755014939741</v>
+        <v>0.871475872668353</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9132283375118718</v>
+        <v>0.9132285659963434</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9934838703184417</v>
+        <v>0.9934838811556498</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8955223880597015</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7745362030026942</v>
+        <v>0.7214686227223229</v>
       </c>
       <c r="L14" t="n">
-        <v>0.648857217595065</v>
+        <v>0.7738184491444068</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7330437711841727</v>
+        <v>0.9657668473509452</v>
       </c>
     </row>
     <row r="15">
@@ -1076,25 +1076,25 @@
         <v>0.9971305595408895</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8814210891723633</v>
+        <v>0.8814220347187736</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9233967129028204</v>
+        <v>0.923397340557792</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9944586049426686</v>
+        <v>0.9944586311325883</v>
       </c>
       <c r="J15" t="n">
         <v>0.9193548387096774</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8046030440927422</v>
+        <v>0.7170866400964798</v>
       </c>
       <c r="L15" t="n">
-        <v>0.619462798399975</v>
+        <v>0.841403705704086</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6975229206090175</v>
+        <v>0.9921447344845341</v>
       </c>
     </row>
     <row r="16">
@@ -1119,25 +1119,25 @@
         <v>0.9964813511611541</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8787075967499705</v>
+        <v>0.8787085224281658</v>
       </c>
       <c r="H16" t="n">
-        <v>0.919520793539105</v>
+        <v>0.9195214302250834</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9950292318156271</v>
+        <v>0.995029190272996</v>
       </c>
       <c r="J16" t="n">
         <v>0.8939393939393939</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7861216688285466</v>
+        <v>0.7213817288480412</v>
       </c>
       <c r="L16" t="n">
-        <v>0.654561252128173</v>
+        <v>0.9548372531717179</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7022672298439534</v>
+        <v>0.9964447279767641</v>
       </c>
     </row>
     <row r="17">
@@ -1162,25 +1162,25 @@
         <v>0.9985935302390999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8816190912868037</v>
+        <v>0.8816207439610453</v>
       </c>
       <c r="H17" t="n">
-        <v>0.923729495568709</v>
+        <v>0.9237308962778612</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9937660378037076</v>
+        <v>0.9937660739277349</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9852941176470589</v>
+        <v>0.9850746268656716</v>
       </c>
       <c r="K17" t="n">
-        <v>0.861776406616016</v>
+        <v>0.8110868750668284</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7008419833249672</v>
+        <v>0.7267420875980196</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9043111800739367</v>
+        <v>0.9629512733220359</v>
       </c>
     </row>
     <row r="18">
@@ -1205,25 +1205,25 @@
         <v>0.9992857142857143</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8824361689162977</v>
+        <v>0.8824362529046608</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9264342658447496</v>
+        <v>0.9264343362866025</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9942582954059948</v>
+        <v>0.9942582683129744</v>
       </c>
       <c r="J18" t="n">
         <v>0.9848484848484849</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8677012944221496</v>
+        <v>0.7995500952908488</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6778866198495263</v>
+        <v>0.781720564419304</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8942716666480064</v>
+        <v>0.9849411986937576</v>
       </c>
     </row>
     <row r="19">
@@ -1248,25 +1248,25 @@
         <v>0.9985652797704447</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8768130432475697</v>
+        <v>0.8768128960421591</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9187373067393447</v>
+        <v>0.9187370186502283</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9933949121923158</v>
+        <v>0.9933949519287456</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8593579605591637</v>
+        <v>0.846683058473799</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6914462398917407</v>
+        <v>0.8270633657014789</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8369234892025902</v>
+        <v>0.9993278451382168</v>
       </c>
     </row>
     <row r="20">
@@ -1291,25 +1291,25 @@
         <v>0.9978479196556671</v>
       </c>
       <c r="G20" t="n">
-        <v>0.881657951708996</v>
+        <v>0.8816585929104777</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9240123476042892</v>
+        <v>0.9240127585150979</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9944654188372872</v>
+        <v>0.9944654350930994</v>
       </c>
       <c r="J20" t="n">
         <v>0.9838709677419355</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8629750433566279</v>
+        <v>0.8112334695554548</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6623952128930243</v>
+        <v>0.8893515476296024</v>
       </c>
       <c r="M20" t="n">
-        <v>0.762747350945273</v>
+        <v>0.9995070742022606</v>
       </c>
     </row>
     <row r="21">
@@ -1334,25 +1334,25 @@
         <v>0.9978888106966924</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8679686324162916</v>
+        <v>0.8679675369551687</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9132801655567053</v>
+        <v>0.9132797022660574</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9920511841773987</v>
+        <v>0.9920511290882573</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8434070751081465</v>
+        <v>0.7930429114988355</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6984517153830373</v>
+        <v>0.9681751274807152</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8441002696546397</v>
+        <v>0.9995812814344059</v>
       </c>
     </row>
     <row r="22">
@@ -1365,37 +1365,37 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.990909090909091</v>
+        <v>0.977511961722488</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9933589653967144</v>
+        <v>0.9832799715403771</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9874913134120917</v>
+        <v>0.9949604031677466</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9992967651195499</v>
+        <v>0.9718706047819972</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8733053704102834</v>
+        <v>0.8733064739993124</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9181070589657986</v>
+        <v>0.9181087125431407</v>
       </c>
       <c r="I22" t="n">
-        <v>0.993099985700665</v>
+        <v>0.993099921580517</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.01492537313432836</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05981391533281448</v>
+        <v>0.0003406194045250881</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5990458847176342</v>
+        <v>0.8663717407788804</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8206950698391674</v>
+        <v>0.5065459226216397</v>
       </c>
     </row>
     <row r="23">
@@ -1408,37 +1408,37 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9956937799043062</v>
+        <v>0.991866028708134</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9967960128159488</v>
+        <v>0.9939652112176074</v>
       </c>
       <c r="E23" t="n">
-        <v>0.99361249112846</v>
+        <v>0.9880028228652082</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8835229756254138</v>
+        <v>0.8835222874626969</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9270111773953293</v>
+        <v>0.9270103691202222</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9943088329199589</v>
+        <v>0.9943088654315833</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1818181818181818</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06171302901589854</v>
+        <v>0.0001211272092364097</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6025237728920295</v>
+        <v>0.9529668059312937</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8012327678424905</v>
+        <v>0.9106464840923295</v>
       </c>
     </row>
     <row r="24">
@@ -1451,37 +1451,37 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9904716531681753</v>
+        <v>0.8275369223439734</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9928469241773963</v>
+        <v>0.8512736236647493</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9900142653352354</v>
+        <v>0.9961538461538462</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9956958393113343</v>
+        <v>0.7431850789096126</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8772216845642437</v>
+        <v>0.877222048513817</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9196531808737552</v>
+        <v>0.9196537091876521</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9932471170569911</v>
+        <v>0.9932471387314074</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3432835820895522</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.09132182640705894</v>
+        <v>0.04250526869817903</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7261994922005698</v>
+        <v>0.8508139155254447</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7138878633511563</v>
+        <v>0.7652167623086523</v>
       </c>
     </row>
     <row r="25">
@@ -1494,37 +1494,37 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9942556247008137</v>
+        <v>0.9937769267592149</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9957050823192556</v>
+        <v>0.9953521630318198</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9935714285714285</v>
+        <v>0.99215965787598</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9978479196556671</v>
+        <v>0.9985652797704447</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8792047663168474</v>
+        <v>0.8792036925301407</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9220201219573165</v>
+        <v>0.9220194247635928</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9943008784091834</v>
+        <v>0.9943008955680963</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.1774193548387097</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05265433497265292</v>
+        <v>0.01147063441431182</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7404948464389892</v>
+        <v>0.9538159200981741</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7489102835869953</v>
+        <v>0.7406992668406137</v>
       </c>
     </row>
     <row r="26">
@@ -1540,34 +1540,34 @@
         <v>0.9914204003813155</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9936930623686054</v>
+        <v>0.9936797752808989</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9895324494068388</v>
+        <v>0.9915907498248073</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9978888106966924</v>
+        <v>0.995777621393385</v>
       </c>
       <c r="G26" t="n">
-        <v>0.858716758814725</v>
+        <v>0.8587157943032004</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9056844873861833</v>
+        <v>0.9056837730335466</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9915337562561035</v>
+        <v>0.9915337544499021</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="K26" t="n">
-        <v>0.05197145378743281</v>
+        <v>0.11019174917954</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7630681486890163</v>
+        <v>0.5918707544125166</v>
       </c>
       <c r="M26" t="n">
-        <v>0.594969161985442</v>
+        <v>0.7188821720636704</v>
       </c>
     </row>
     <row r="27">
@@ -1592,25 +1592,25 @@
         <v>0.9789029535864979</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8463050614703785</v>
+        <v>0.8463051391370369</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8945630924268202</v>
+        <v>0.8945628260121201</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9895165445226611</v>
+        <v>0.9895165770342855</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9852941176470589</v>
+        <v>0.9850746268656716</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4867276175146267</v>
+        <v>0.7157946791666657</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6886922259499971</v>
+        <v>0.994123690280674</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7328255647758202</v>
+        <v>0.9982706365300649</v>
       </c>
     </row>
     <row r="28">
@@ -1635,25 +1635,25 @@
         <v>0.9892857142857143</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8605045911037561</v>
+        <v>0.8605053578362321</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9091603096687433</v>
+        <v>0.9091611829670992</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9898719769535642</v>
+        <v>0.9898719670194568</v>
       </c>
       <c r="J28" t="n">
         <v>0.9696969696969697</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4912294041184536</v>
+        <v>0.744289778398745</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5905566504456556</v>
+        <v>0.706494008169657</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8336188476387573</v>
+        <v>0.9779416504908691</v>
       </c>
     </row>
     <row r="29">
@@ -1678,25 +1678,25 @@
         <v>0.9849354375896701</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8565261725223425</v>
+        <v>0.8565254834565249</v>
       </c>
       <c r="H29" t="n">
-        <v>0.903375425122001</v>
+        <v>0.9033742628314279</v>
       </c>
       <c r="I29" t="n">
-        <v>0.990618266842582</v>
+        <v>0.9906183056759111</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9402985074626866</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5078389279709586</v>
+        <v>0.7981758410968478</v>
       </c>
       <c r="L29" t="n">
-        <v>0.6440860684181692</v>
+        <v>0.902722780104904</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6805233095185674</v>
+        <v>0.9897552401359592</v>
       </c>
     </row>
     <row r="30">
@@ -1721,25 +1721,25 @@
         <v>0.9870875179340028</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8562777512001268</v>
+        <v>0.8562763315258604</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9042459175442205</v>
+        <v>0.9042453756838134</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9911562944903518</v>
+        <v>0.9911563008120565</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0.473931507997372</v>
+        <v>0.764423580659974</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6121983175323169</v>
+        <v>0.8441047184636362</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6979047227105561</v>
+        <v>0.9961394538562145</v>
       </c>
     </row>
     <row r="31">
@@ -1764,25 +1764,25 @@
         <v>0.9859254046446164</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8467284630645405</v>
+        <v>0.8467286789056027</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8954408186854739</v>
+        <v>0.8954414644024589</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9875855509078864</v>
+        <v>0.9875855463923831</v>
       </c>
       <c r="J31" t="n">
         <v>0.9848484848484849</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4550437806827413</v>
+        <v>0.689455161718016</v>
       </c>
       <c r="L31" t="n">
-        <v>0.6374063683992991</v>
+        <v>0.9140555433702972</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6934958276718377</v>
+        <v>0.9984681319029098</v>
       </c>
     </row>
     <row r="32">
@@ -1795,37 +1795,37 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6803827751196172</v>
+        <v>0.9832535885167464</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8097949886104784</v>
+        <v>0.9876281371509368</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6803827751196172</v>
+        <v>0.9928926794598436</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.9824191279887482</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8532908694310621</v>
+        <v>0.8532926711169156</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9010918790643866</v>
+        <v>0.9010935407696348</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9901556101712313</v>
+        <v>0.9901556481014598</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9852941176470589</v>
+        <v>0.9850746268656716</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7997198334712613</v>
+        <v>0.7180227819107362</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6405552611340455</v>
+        <v>0.8012049634537596</v>
       </c>
       <c r="M32" t="n">
-        <v>0.7645014514783397</v>
+        <v>0.9881103306452731</v>
       </c>
     </row>
     <row r="33">
@@ -1838,37 +1838,37 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9822966507177033</v>
+        <v>0.9866028708133971</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9869026548672566</v>
+        <v>0.9899856938483548</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9782456140350877</v>
+        <v>0.9914040114613181</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9957142857142857</v>
+        <v>0.9885714285714285</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8633684100526752</v>
+        <v>0.8633690015836195</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9113046337257732</v>
+        <v>0.9113050798575083</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9901921017603441</v>
+        <v>0.9901920611208136</v>
       </c>
       <c r="J33" t="n">
         <v>0.9848484848484849</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8529408520571241</v>
+        <v>0.7923322744441755</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6681943285919574</v>
+        <v>0.8106304518295943</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7762667690227975</v>
+        <v>0.9874986449708089</v>
       </c>
     </row>
     <row r="34">
@@ -1881,37 +1881,37 @@
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9814197236779418</v>
+        <v>0.9880895664602192</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9861357980803412</v>
+        <v>0.9910490511994271</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9774489076814659</v>
+        <v>0.9892780557541101</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9949784791965567</v>
+        <v>0.9928263988522238</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8616864726398931</v>
+        <v>0.8616867471824993</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9083558438402234</v>
+        <v>0.9083559522123048</v>
       </c>
       <c r="I34" t="n">
-        <v>0.990698314074314</v>
+        <v>0.9906983492952405</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9402985074626866</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8273620401371161</v>
+        <v>0.7894663836747881</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6221430773353984</v>
+        <v>0.8094989492033844</v>
       </c>
       <c r="M34" t="n">
-        <v>0.7739890212946341</v>
+        <v>0.9901698727456348</v>
       </c>
     </row>
     <row r="35">
@@ -1924,37 +1924,37 @@
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6692197223551939</v>
+        <v>0.9851603638104356</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8013797068123024</v>
+        <v>0.988820771727371</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6685851318944844</v>
+        <v>0.9941986947063089</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.9835007173601148</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8564600474906691</v>
+        <v>0.8564598190061974</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9041051602724827</v>
+        <v>0.9041048234159296</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9910348509297227</v>
+        <v>0.9910348635731321</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8335026076686457</v>
+        <v>0.7637047988753165</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6337797647154865</v>
+        <v>0.8284028592033146</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7562754802424461</v>
+        <v>0.9887612964597442</v>
       </c>
     </row>
     <row r="36">
@@ -1967,37 +1967,682 @@
         <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9809342230695901</v>
+        <v>0.9823641563393708</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9860917941585535</v>
+        <v>0.9869764167546639</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9745704467353952</v>
+        <v>0.9873239436619718</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9978888106966924</v>
+        <v>0.9866291344123856</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8423036373022831</v>
+        <v>0.8423028181899678</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8919422400720192</v>
+        <v>0.8919416702154911</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9872301708568226</v>
+        <v>0.9872301383451982</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7929164512096567</v>
+        <v>0.7165410940283565</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5778441695441866</v>
+        <v>0.68486269576154</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7813530426472427</v>
+        <v>0.9807849804645009</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MAAL_V5</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.9818181818181818</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.9865439093484419</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9935805991440799</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9796061884669479</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8582855372717886</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.904884238134731</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9901412725448608</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9701492537313433</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.756092082875878</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.5414173372207365</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.9547086064264165</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MAAL_V5</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9889952153110048</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.9917769038255273</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9928418038654259</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9907142857142858</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.8600490598967581</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.9090981212529269</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9901176040822809</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.7551828254804467</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.5702815145953398</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.9475124077467516</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MAAL_V5</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9895188184849929</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.9921146953405018</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9914040114613181</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9928263988522238</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.8552634129018495</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.9024570141777848</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9904165358254404</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.8196724284262884</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.8454892281613114</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.9994592275884416</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MAAL_V5</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.987075155576831</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9903121636167922</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.990667623833453</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9899569583931134</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.8610182260022019</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9073403071273457</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9914258059227106</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.7743437520919307</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.8395756019201908</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.9989376371906649</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MAAL_V5</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.9833174451858914</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.9876456053653371</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9907932011331445</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.9845179451090781</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.8460581465200945</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8942658269044125</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9876396728284431</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.7399466290056192</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.7518836962951437</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9739596173237783</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MAAL_V6</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.9822966507177033</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.9869488536155203</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9900920028308563</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.9838255977496484</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.8557823137803511</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.9033143249425021</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.990009886748863</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9701492537313433</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.7485296744019238</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.9146829864095789</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9962396020333825</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MAAL_V6</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.9875598086124402</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.9907010014306151</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.9921203438395415</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9892857142857143</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.8621845498229518</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.9101363574013566</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9903853156349876</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.7508468379577001</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.6813178575557135</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9802194664819223</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MAAL_V6</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.9838018103858981</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.9877785765636233</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9899135446685879</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.9856527977044476</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.8577874591856292</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.904851518797152</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.9905532174038164</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.7981004362541532</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.9496280820426782</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.99615513176199</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MAAL_V6</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9851603638104356</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.9888849049838652</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9885304659498207</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9892395982783357</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.8584907551606497</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.9055369415066459</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.9910281174110643</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.7533918616752471</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.7427340503264972</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.9661562062739846</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MAAL_V6</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9814108674928503</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.986233674549947</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9893767705382436</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.9831104855735397</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.8445062312212858</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.8930819043607423</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.987387043057066</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.7205980168375492</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.988632921491411</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.9939118138247676</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MAAL_V7</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.9846889952153111</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.9887244538407329</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.990819209039548</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9866385372714487</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.8552846466050004</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.9023047396630952</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.9901188033999819</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.9850746268656716</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.7564414675111202</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.5458042246849366</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.9453978699979064</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MAAL_V7</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.9885167464114832</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.9914224446032881</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9921316165951359</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9907142857142858</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.8635942195401047</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9114910382213015</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9902360529610605</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.8003538070303021</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.8217288813182236</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.991422844484491</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MAAL_V7</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.9852310624106717</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.9888769285970578</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9892318736539842</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9885222381635581</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.8559718755158511</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9029714654792439</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.9902262669621091</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.8161451319853464</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.8270377776839645</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.9881559544715972</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MAAL_V7</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.9856390617520344</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.9892163910855499</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9913544668587896</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.9870875179340028</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.860923991058812</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.9076077649087617</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9911485169873093</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.8025895534984527</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.8073153494640382</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.9879068211682382</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MAAL_V7</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.982840800762631</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.9873150105708245</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.9887085391672548</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.9859254046446164</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8476984148675745</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.8966762938282706</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9872894431605483</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.7689103448031916</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.8732982236024602</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.9978820780588483</v>
       </c>
     </row>
   </sheetData>

--- a/resultados_cluster/evaluated_metrics_detailed.xlsx
+++ b/resultados_cluster/evaluated_metrics_detailed.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Experiment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Fold</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>F1-Score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>IoU</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Dice</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Pixel Accuracy</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pointing Game</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Saliency IoU</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Deletion Score (AUC)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Insertion Score (AUC)</t>
         </is>
@@ -1143,7 +1131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fusion_CAM</t>
+          <t>MAAL</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1186,7 +1174,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fusion_CAM</t>
+          <t>MAAL</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1229,7 +1217,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fusion_CAM</t>
+          <t>MAAL</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1272,7 +1260,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fusion_CAM</t>
+          <t>MAAL</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1315,7 +1303,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fusion_CAM</t>
+          <t>MAAL</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1358,7 +1346,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MAAL</t>
+          <t>MAAL_V2</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1401,7 +1389,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MAAL</t>
+          <t>MAAL_V2</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1444,7 +1432,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MAAL</t>
+          <t>MAAL_V2</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1487,7 +1475,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MAAL</t>
+          <t>MAAL_V2</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1530,7 +1518,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MAAL</t>
+          <t>MAAL_V2</t>
         </is>
       </c>
       <c r="B26" t="n">
